--- a/jogos_2024-12-10.xlsx
+++ b/jogos_2024-12-10.xlsx
@@ -1417,19 +1417,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI8" t="n">
         <v>3.1</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X8" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45636.61458333334</v>
@@ -1546,19 +1546,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="M9" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.44</v>
       </c>
-      <c r="O9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="V9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z9" t="n">
         <v>2.05</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.29</v>
-      </c>
       <c r="AA9" t="n">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AH9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI9" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45636.61458333334</v>
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="T10" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.53</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>1.62</v>
+        <v>2.88</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45636.69791666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,16 +1804,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
         <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AA11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['46', '54']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['68']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45636.69791666666</v>
@@ -1933,16 +1933,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
         <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="R12" t="n">
         <v>1.44</v>
@@ -1983,59 +1983,59 @@
         <v>2.63</v>
       </c>
       <c r="T12" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V12" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['90+3']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['62']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45636.69791666666</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="M13" t="n">
         <v>3.3</v>
       </c>
       <c r="N13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S13" t="n">
         <v>3.4</v>
       </c>
-      <c r="O13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
         <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X13" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['24', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45636.69791666666</v>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,22 +2217,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.7</v>
+        <v>3.75</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="O14" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
         <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="R14" t="n">
         <v>1.44</v>
@@ -2247,53 +2247,53 @@
         <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="X14" t="n">
-        <v>2.95</v>
+        <v>3.55</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AD14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['44', '60']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>3</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45636.69791666666</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,22 +2346,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.75</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="P15" t="n">
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.88</v>
+        <v>5.5</v>
       </c>
       <c r="R15" t="n">
         <v>1.44</v>
@@ -2376,53 +2376,53 @@
         <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W15" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="X15" t="n">
-        <v>3.55</v>
+        <v>2.95</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['44', '60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.85</v>
+        <v>1.16</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45636.69791666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2464,7 +2464,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="M16" t="n">
         <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T16" t="n">
         <v>3</v>
       </c>
-      <c r="P16" t="n">
+      <c r="U16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['24', '90']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['46', '54']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['43']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>2</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45636.69791666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,16 +2578,16 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
@@ -2596,7 +2596,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>2.88</v>
       </c>
       <c r="M17" t="n">
         <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
         <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.1</v>
+        <v>2.61</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AC17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['24', '84']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['14', '74', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['54']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45636.70833333334</v>
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,22 +2733,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O18" t="n">
         <v>3.1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.75</v>
       </c>
       <c r="P18" t="n">
         <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
         <v>1.33</v>
@@ -2766,50 +2766,50 @@
         <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['27', '62']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '52', '85']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45636.70833333334</v>
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>17</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="N20" t="n">
-        <v>2.63</v>
+        <v>1.14</v>
       </c>
       <c r="O20" t="n">
+        <v>13</v>
+      </c>
+      <c r="P20" t="n">
         <v>3.1</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.72</v>
+        <v>1.91</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['27', '62']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['3', '52', '85']</t>
+          <t>['11', '45', '70', '87', '90+3']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.52</v>
+        <v>5.75</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.54</v>
+        <v>1.02</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.83</v>
+        <v>5.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45636.70833333334</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>17</v>
+        <v>2.7</v>
       </c>
       <c r="M21" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>1.14</v>
+        <v>2.4</v>
       </c>
       <c r="O21" t="n">
-        <v>13</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.44</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="U21" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
-        <v>6.6</v>
+        <v>4.85</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.91</v>
+        <v>2.53</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['45+2', '65']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['11', '45', '70', '87', '90+3']</t>
+          <t>['10', '56', '59']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>5.75</v>
+        <v>1.59</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45636.70833333334</v>
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,28 +3249,28 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="P22" t="n">
         <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
         <v>2.5</v>
@@ -3279,53 +3279,53 @@
         <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X22" t="n">
-        <v>4.7</v>
+        <v>4.35</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Z22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['24', '84']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['3']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.67</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45636.70833333334</v>
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.7</v>
+        <v>7.5</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>5.75</v>
       </c>
       <c r="N23" t="n">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="O23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['30', '72', '85']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
         <v>3.2</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['45+2', '65']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['10', '56', '59']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.49</v>
+        <v>1.08</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45636.70833333334</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>7.5</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>5.75</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.33</v>
       </c>
-      <c r="O24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['14', '74', '90+2']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.22</v>
       </c>
-      <c r="S24" t="n">
-        <v>4</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['30', '72', '85']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.08</v>
+        <v>2.05</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.5</v>
+        <v>1.53</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.29</v>
+        <v>2.63</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45636.70833333334</v>
